--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\wsp.p\tochka-dev-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4921ABB1-9B22-4F81-AD8C-759F2C2AE10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D088986-D663-4429-AE9F-16A2E14A318B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{3BA05377-DF0C-404B-804F-25852582BFD9}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId2"/>
+    <pivotCache cacheId="8" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TS" refreshedDate="46147.37800798611" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="56" xr:uid="{C5E323F3-16D3-450F-8C47-505DDB253939}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TS" refreshedDate="46147.385649768519" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="56" xr:uid="{C5E323F3-16D3-450F-8C47-505DDB253939}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K57" sheet="Лист1"/>
   </cacheSource>
@@ -282,19 +282,19 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.94711538461538458" maxValue="10400"/>
     </cacheField>
     <cacheField name="Тест" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="5250"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="5030"/>
     </cacheField>
     <cacheField name="Деньги" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2500" maxValue="395000"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2500" maxValue="414500"/>
     </cacheField>
     <cacheField name="Себест" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1745" maxValue="2690"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1695" maxValue="2690"/>
     </cacheField>
     <cacheField name="Прох/огр" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="40" maxValue="400"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="41.666666666666664" maxValue="600"/>
     </cacheField>
     <cacheField name="Ден/Себ" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.92936802973977695" maxValue="6.6852367688022287"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.92936802973977695" maxValue="6.9637883008356543"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -337,8 +337,8 @@
     <n v="214"/>
     <n v="171"/>
     <n v="9850"/>
-    <n v="5250"/>
-    <n v="395000"/>
+    <n v="5030"/>
+    <n v="414500"/>
     <m/>
     <m/>
     <m/>
@@ -349,7 +349,7 @@
     <n v="0.41153846153846152"/>
     <n v="0.32884615384615384"/>
     <n v="0.94711538461538458"/>
-    <n v="2.5240384615384617"/>
+    <n v="2.4182692307692308"/>
     <m/>
     <m/>
     <m/>
@@ -434,10 +434,10 @@
     <n v="8"/>
     <n v="230"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="1970"/>
-    <n v="400"/>
-    <n v="2.030456852791878"/>
+    <n v="600"/>
+    <n v="3.0456852791878171"/>
   </r>
   <r>
     <x v="8"/>
@@ -446,10 +446,10 @@
     <n v="1"/>
     <n v="240"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="2040"/>
-    <n v="400"/>
-    <n v="1.9607843137254901"/>
+    <n v="600"/>
+    <n v="2.9411764705882355"/>
   </r>
   <r>
     <x v="9"/>
@@ -458,10 +458,10 @@
     <n v="2"/>
     <n v="250"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="2140"/>
-    <n v="400"/>
-    <n v="1.8691588785046729"/>
+    <n v="600"/>
+    <n v="2.8037383177570092"/>
   </r>
   <r>
     <x v="10"/>
@@ -470,10 +470,10 @@
     <n v="4"/>
     <n v="220"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="1910"/>
-    <n v="400"/>
-    <n v="2.0942408376963351"/>
+    <n v="600"/>
+    <n v="3.1413612565445028"/>
   </r>
   <r>
     <x v="11"/>
@@ -482,10 +482,10 @@
     <n v="3"/>
     <n v="230"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="1965"/>
-    <n v="400"/>
-    <n v="2.0356234096692112"/>
+    <n v="600"/>
+    <n v="3.053435114503817"/>
   </r>
   <r>
     <x v="12"/>
@@ -494,10 +494,10 @@
     <n v="2"/>
     <n v="220"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="1860"/>
-    <n v="400"/>
-    <n v="2.150537634408602"/>
+    <n v="600"/>
+    <n v="3.225806451612903"/>
   </r>
   <r>
     <x v="13"/>
@@ -506,10 +506,10 @@
     <n v="8"/>
     <n v="240"/>
     <n v="10"/>
-    <n v="4000"/>
+    <n v="6000"/>
     <n v="2055"/>
-    <n v="400"/>
-    <n v="1.9464720194647203"/>
+    <n v="600"/>
+    <n v="2.9197080291970803"/>
   </r>
   <r>
     <x v="14"/>
@@ -589,11 +589,11 @@
     <n v="8"/>
     <n v="1"/>
     <n v="200"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1825"/>
-    <n v="200"/>
-    <n v="3.2876712328767121"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1775"/>
+    <n v="400"/>
+    <n v="4.507042253521127"/>
   </r>
   <r>
     <x v="21"/>
@@ -601,11 +601,11 @@
     <n v="1"/>
     <n v="2"/>
     <n v="210"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1890"/>
-    <n v="200"/>
-    <n v="3.1746031746031744"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1840"/>
+    <n v="400"/>
+    <n v="4.3478260869565215"/>
   </r>
   <r>
     <x v="22"/>
@@ -613,11 +613,11 @@
     <n v="2"/>
     <n v="4"/>
     <n v="200"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1830"/>
-    <n v="200"/>
-    <n v="3.278688524590164"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1780"/>
+    <n v="400"/>
+    <n v="4.4943820224719104"/>
   </r>
   <r>
     <x v="23"/>
@@ -625,11 +625,11 @@
     <n v="4"/>
     <n v="3"/>
     <n v="190"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1745"/>
-    <n v="200"/>
-    <n v="3.4383954154727792"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1695"/>
+    <n v="400"/>
+    <n v="4.71976401179941"/>
   </r>
   <r>
     <x v="24"/>
@@ -637,11 +637,11 @@
     <n v="6"/>
     <n v="2"/>
     <n v="200"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1845"/>
-    <n v="200"/>
-    <n v="3.2520325203252032"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1795"/>
+    <n v="400"/>
+    <n v="4.4568245125348191"/>
   </r>
   <r>
     <x v="25"/>
@@ -649,11 +649,11 @@
     <n v="8"/>
     <n v="8"/>
     <n v="210"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1940"/>
-    <n v="200"/>
-    <n v="3.0927835051546393"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1890"/>
+    <n v="400"/>
+    <n v="4.2328042328042326"/>
   </r>
   <r>
     <x v="26"/>
@@ -661,11 +661,11 @@
     <n v="1"/>
     <n v="1"/>
     <n v="200"/>
-    <n v="30"/>
-    <n v="6000"/>
-    <n v="1785"/>
-    <n v="200"/>
-    <n v="3.3613445378151261"/>
+    <n v="20"/>
+    <n v="8000"/>
+    <n v="1735"/>
+    <n v="400"/>
+    <n v="4.6109510086455332"/>
   </r>
   <r>
     <x v="27"/>
@@ -745,11 +745,11 @@
     <n v="4"/>
     <n v="2"/>
     <n v="180"/>
-    <n v="125"/>
-    <n v="10000"/>
-    <n v="2125"/>
+    <n v="100"/>
+    <n v="8000"/>
+    <n v="2000"/>
     <n v="80"/>
-    <n v="4.7058823529411766"/>
+    <n v="4"/>
   </r>
   <r>
     <x v="34"/>
@@ -757,11 +757,11 @@
     <n v="6"/>
     <n v="4"/>
     <n v="170"/>
-    <n v="125"/>
-    <n v="10000"/>
-    <n v="2080"/>
+    <n v="100"/>
+    <n v="8000"/>
+    <n v="1955"/>
     <n v="80"/>
-    <n v="4.8076923076923075"/>
+    <n v="4.0920716112531972"/>
   </r>
   <r>
     <x v="35"/>
@@ -769,11 +769,11 @@
     <n v="8"/>
     <n v="3"/>
     <n v="160"/>
-    <n v="125"/>
-    <n v="10000"/>
-    <n v="2010"/>
+    <n v="100"/>
+    <n v="8000"/>
+    <n v="1885"/>
     <n v="80"/>
-    <n v="4.9751243781094523"/>
+    <n v="4.2440318302387272"/>
   </r>
   <r>
     <x v="36"/>
@@ -781,11 +781,11 @@
     <n v="1"/>
     <n v="2"/>
     <n v="190"/>
-    <n v="125"/>
-    <n v="10000"/>
-    <n v="2200"/>
+    <n v="100"/>
+    <n v="8000"/>
+    <n v="2075"/>
     <n v="80"/>
-    <n v="4.5454545454545459"/>
+    <n v="3.8554216867469879"/>
   </r>
   <r>
     <x v="37"/>
@@ -793,11 +793,11 @@
     <n v="2"/>
     <n v="8"/>
     <n v="180"/>
-    <n v="125"/>
-    <n v="10000"/>
-    <n v="2170"/>
+    <n v="100"/>
+    <n v="8000"/>
+    <n v="2045"/>
     <n v="80"/>
-    <n v="4.6082949308755756"/>
+    <n v="3.9119804400977993"/>
   </r>
   <r>
     <x v="38"/>
@@ -805,11 +805,11 @@
     <n v="4"/>
     <n v="1"/>
     <n v="170"/>
-    <n v="125"/>
-    <n v="10000"/>
-    <n v="2040"/>
+    <n v="100"/>
+    <n v="8000"/>
+    <n v="1915"/>
     <n v="80"/>
-    <n v="4.9019607843137258"/>
+    <n v="4.1775456919060057"/>
   </r>
   <r>
     <x v="39"/>
@@ -902,10 +902,10 @@
     <n v="4"/>
     <n v="70"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="2115"/>
-    <n v="40"/>
-    <n v="5.6737588652482271"/>
+    <n v="41.666666666666664"/>
+    <n v="5.9101654846335698"/>
   </r>
   <r>
     <x v="47"/>
@@ -914,10 +914,10 @@
     <n v="3"/>
     <n v="50"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="1970"/>
-    <n v="40"/>
-    <n v="6.0913705583756341"/>
+    <n v="41.666666666666664"/>
+    <n v="6.345177664974619"/>
   </r>
   <r>
     <x v="48"/>
@@ -926,10 +926,10 @@
     <n v="2"/>
     <n v="60"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="2045"/>
-    <n v="40"/>
-    <n v="5.8679706601466997"/>
+    <n v="41.666666666666664"/>
+    <n v="6.1124694376528117"/>
   </r>
   <r>
     <x v="49"/>
@@ -938,10 +938,10 @@
     <n v="2"/>
     <n v="50"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="1970"/>
-    <n v="40"/>
-    <n v="6.0913705583756341"/>
+    <n v="41.666666666666664"/>
+    <n v="6.345177664974619"/>
   </r>
   <r>
     <x v="50"/>
@@ -950,10 +950,10 @@
     <n v="8"/>
     <n v="40"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="1945"/>
-    <n v="40"/>
-    <n v="6.1696658097686372"/>
+    <n v="41.666666666666664"/>
+    <n v="6.4267352185089974"/>
   </r>
   <r>
     <x v="51"/>
@@ -962,10 +962,10 @@
     <n v="1"/>
     <n v="50"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="1975"/>
-    <n v="40"/>
-    <n v="6.075949367088608"/>
+    <n v="41.666666666666664"/>
+    <n v="6.3291139240506329"/>
   </r>
   <r>
     <x v="52"/>
@@ -974,16 +974,16 @@
     <n v="4"/>
     <n v="30"/>
     <n v="300"/>
-    <n v="12000"/>
+    <n v="12500"/>
     <n v="1795"/>
-    <n v="40"/>
-    <n v="6.6852367688022287"/>
+    <n v="41.666666666666664"/>
+    <n v="6.9637883008356543"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{843CAD5B-8087-419E-B183-9C4507CC2B27}" name="Сводная таблица2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{843CAD5B-8087-419E-B183-9C4507CC2B27}" name="Сводная таблица2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Q5:R58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -1095,10 +1095,10 @@
       <x v="41"/>
     </i>
     <i>
-      <x v="37"/>
+      <x v="40"/>
     </i>
     <i>
-      <x v="40"/>
+      <x v="37"/>
     </i>
     <i>
       <x v="43"/>
@@ -1107,13 +1107,52 @@
       <x v="39"/>
     </i>
     <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
       <x v="33"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="30"/>
     </i>
     <i>
       <x v="36"/>
     </i>
     <i>
-      <x v="42"/>
+      <x v="27"/>
     </i>
     <i>
       <x v="32"/>
@@ -1128,52 +1167,31 @@
       <x v="34"/>
     </i>
     <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
       <x v="16"/>
     </i>
     <i>
-      <x v="19"/>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="8"/>
     </i>
     <i>
       <x v="15"/>
     </i>
     <i>
-      <x v="23"/>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i>
       <x v="13"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="11"/>
     </i>
     <i>
       <x v="14"/>
@@ -1182,28 +1200,10 @@
       <x v="17"/>
     </i>
     <i>
-      <x v="12"/>
+      <x v="7"/>
     </i>
     <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="7"/>
+      <x v="12"/>
     </i>
     <i>
       <x v="2"/>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="G4" s="1">
         <f t="shared" si="1"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="H4" s="1">
         <f t="shared" si="1"/>
-        <v>395000</v>
+        <v>414500</v>
       </c>
       <c r="R4" s="11"/>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G5" s="6">
         <f t="shared" si="2"/>
-        <v>2.5240384615384617</v>
+        <v>2.4182692307692308</v>
       </c>
       <c r="H5" s="1"/>
       <c r="Q5" s="9" t="s">
@@ -1787,7 +1787,7 @@
         <v>51</v>
       </c>
       <c r="R6" s="13">
-        <v>6.6852367688022287</v>
+        <v>6.9637883008356543</v>
       </c>
       <c r="S6">
         <f>VLOOKUP($Q6,$B$6:$M$57,5,FALSE)</f>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="U6">
         <f>VLOOKUP($Q6,$B$6:$M$57,7,FALSE)</f>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V6">
         <f ca="1">VLOOKUP($Q6,$B$6:$M$57,8,FALSE)</f>
@@ -1807,11 +1807,11 @@
       </c>
       <c r="W6">
         <f ca="1">VLOOKUP($Q6,$B$6:$M$57,9,FALSE)</f>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X6">
         <f ca="1">OFFSET(X6,-1,0)+OFFSET(X6,0,-3)</f>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="Y6">
         <f ca="1">OFFSET(Y6,-1,0)+OFFSET(Y6,0,-5)</f>
@@ -1875,7 +1875,7 @@
         <v>49</v>
       </c>
       <c r="R7" s="13">
-        <v>6.1696658097686372</v>
+        <v>6.4267352185089974</v>
       </c>
       <c r="S7">
         <f t="shared" ref="S7:S57" si="7">VLOOKUP($Q7,$B$6:$M$57,5,FALSE)</f>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="U7">
         <f t="shared" ref="U7:U57" si="9">VLOOKUP($Q7,$B$6:$M$57,7,FALSE)</f>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V7">
         <f t="shared" ref="V7:V57" ca="1" si="10">VLOOKUP($Q7,$B$6:$M$57,8,FALSE)</f>
@@ -1895,11 +1895,11 @@
       </c>
       <c r="W7">
         <f t="shared" ref="W7:W57" ca="1" si="11">VLOOKUP($Q7,$B$6:$M$57,9,FALSE)</f>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X7">
         <f t="shared" ref="X7:X57" ca="1" si="12">OFFSET(X7,-1,0)+OFFSET(X7,0,-3)</f>
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="Y7">
         <f t="shared" ref="Y7:Z57" ca="1" si="13">OFFSET(Y7,-1,0)+OFFSET(Y7,0,-5)</f>
@@ -1963,7 +1963,7 @@
         <v>48</v>
       </c>
       <c r="R8" s="13">
-        <v>6.0913705583756341</v>
+        <v>6.345177664974619</v>
       </c>
       <c r="S8">
         <f t="shared" si="7"/>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="U8">
         <f t="shared" si="9"/>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V8">
         <f t="shared" ca="1" si="10"/>
@@ -1983,11 +1983,11 @@
       </c>
       <c r="W8">
         <f t="shared" ca="1" si="11"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X8">
         <f t="shared" ca="1" si="12"/>
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="Y8">
         <f t="shared" ca="1" si="13"/>
@@ -2051,7 +2051,7 @@
         <v>46</v>
       </c>
       <c r="R9" s="13">
-        <v>6.0913705583756341</v>
+        <v>6.345177664974619</v>
       </c>
       <c r="S9">
         <f t="shared" si="7"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="U9">
         <f t="shared" si="9"/>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V9">
         <f t="shared" ca="1" si="10"/>
@@ -2071,11 +2071,11 @@
       </c>
       <c r="W9">
         <f t="shared" ca="1" si="11"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X9">
         <f t="shared" ca="1" si="12"/>
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="Y9">
         <f t="shared" ca="1" si="13"/>
@@ -2139,7 +2139,7 @@
         <v>50</v>
       </c>
       <c r="R10" s="13">
-        <v>6.075949367088608</v>
+        <v>6.3291139240506329</v>
       </c>
       <c r="S10">
         <f t="shared" si="7"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="U10">
         <f t="shared" si="9"/>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V10">
         <f t="shared" ca="1" si="10"/>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="W10">
         <f t="shared" ca="1" si="11"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X10">
         <f t="shared" ca="1" si="12"/>
-        <v>60000</v>
+        <v>62500</v>
       </c>
       <c r="Y10">
         <f t="shared" ca="1" si="13"/>
@@ -2227,7 +2227,7 @@
         <v>47</v>
       </c>
       <c r="R11" s="13">
-        <v>5.8679706601466997</v>
+        <v>6.1124694376528117</v>
       </c>
       <c r="S11">
         <f t="shared" si="7"/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="U11">
         <f t="shared" si="9"/>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V11">
         <f t="shared" ca="1" si="10"/>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="W11">
         <f t="shared" ca="1" si="11"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X11">
         <f t="shared" ca="1" si="12"/>
-        <v>72000</v>
+        <v>75000</v>
       </c>
       <c r="Y11">
         <f t="shared" ca="1" si="13"/>
@@ -2289,7 +2289,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2297,15 +2297,15 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K12" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>2.030456852791878</v>
+        <v>3.0456852791878171</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="M12" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="N12" s="4">
         <f ca="1">OFFSET(N12,-1,0)+OFFSET(N12,0,-6)</f>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="O12" s="4">
         <f ca="1">OFFSET(O12,-1,0)+OFFSET(O12,0,-8)</f>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="R12" s="13">
-        <v>5.6737588652482271</v>
+        <v>5.9101654846335698</v>
       </c>
       <c r="S12">
         <f t="shared" si="7"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="U12">
         <f t="shared" si="9"/>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="V12">
         <f t="shared" ca="1" si="10"/>
@@ -2343,11 +2343,11 @@
       </c>
       <c r="W12">
         <f t="shared" ca="1" si="11"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="X12">
         <f t="shared" ca="1" si="12"/>
-        <v>84000</v>
+        <v>87500</v>
       </c>
       <c r="Y12">
         <f t="shared" ca="1" si="13"/>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AD12" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,2,8,230,10,4000],</v>
+        <v>[6,2,8,230,10,6000],</v>
       </c>
       <c r="AG12" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2385,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2393,15 +2393,15 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K13" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9607843137254901</v>
+        <v>2.9411764705882355</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="M13" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="N13" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="O13" s="4">
         <f t="shared" ref="O13:O57" ca="1" si="17">OFFSET(O13,-1,0)+OFFSET(O13,0,-8)</f>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="X13">
         <f t="shared" ca="1" si="12"/>
-        <v>94000</v>
+        <v>97500</v>
       </c>
       <c r="Y13">
         <f t="shared" ca="1" si="13"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="AD13" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[9,4,1,240,10,4000],</v>
+        <v>[9,4,1,240,10,6000],</v>
       </c>
       <c r="AG13" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2489,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="H14" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2497,15 +2497,15 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8691588785046729</v>
+        <v>2.8037383177570092</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>27000</v>
+        <v>33000</v>
       </c>
       <c r="M14" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="N14" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="O14" s="4">
         <f t="shared" ca="1" si="17"/>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="X14">
         <f t="shared" ca="1" si="12"/>
-        <v>104000</v>
+        <v>107500</v>
       </c>
       <c r="Y14">
         <f t="shared" ca="1" si="13"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AD14" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[10,6,2,250,10,4000],</v>
+        <v>[10,6,2,250,10,6000],</v>
       </c>
       <c r="AG14" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2593,7 +2593,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2601,15 +2601,15 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K15" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>2.0942408376963351</v>
+        <v>3.1413612565445028</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>31000</v>
+        <v>39000</v>
       </c>
       <c r="M15" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2617,14 +2617,14 @@
       </c>
       <c r="N15" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="O15" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>40</v>
       </c>
       <c r="Q15" s="10">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="R15" s="13">
         <v>5.1413881748071981</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="X15">
         <f t="shared" ca="1" si="12"/>
-        <v>114000</v>
+        <v>117500</v>
       </c>
       <c r="Y15">
         <f t="shared" ca="1" si="13"/>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AD15" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[8,8,4,220,10,4000],</v>
+        <v>[8,8,4,220,10,6000],</v>
       </c>
       <c r="AG15" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2697,7 +2697,7 @@
         <v>10</v>
       </c>
       <c r="H16" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2705,15 +2705,15 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>2.0356234096692112</v>
+        <v>3.053435114503817</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>35000</v>
+        <v>45000</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2721,14 +2721,14 @@
       </c>
       <c r="N16" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="O16" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>50</v>
       </c>
       <c r="Q16" s="10">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R16" s="13">
         <v>5.1413881748071981</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="X16">
         <f t="shared" ca="1" si="12"/>
-        <v>124000</v>
+        <v>127500</v>
       </c>
       <c r="Y16">
         <f t="shared" ca="1" si="13"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AD16" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[11,1,3,230,10,4000],</v>
+        <v>[11,1,3,230,10,6000],</v>
       </c>
       <c r="AG16" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="H17" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2809,15 +2809,15 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K17" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>2.150537634408602</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>39000</v>
+        <v>51000</v>
       </c>
       <c r="M17" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="N17" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>24000</v>
+        <v>36000</v>
       </c>
       <c r="O17" s="4">
         <f t="shared" ca="1" si="17"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="X17">
         <f t="shared" ca="1" si="12"/>
-        <v>134000</v>
+        <v>137500</v>
       </c>
       <c r="Y17">
         <f t="shared" ca="1" si="13"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AD17" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,2,2,220,10,4000],</v>
+        <v>[6,2,2,220,10,6000],</v>
       </c>
       <c r="AG17" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2905,7 +2905,7 @@
         <v>10</v>
       </c>
       <c r="H18" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2913,15 +2913,15 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K18" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9464720194647203</v>
+        <v>2.9197080291970803</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>43000</v>
+        <v>57000</v>
       </c>
       <c r="M18" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="N18" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>28000</v>
+        <v>42000</v>
       </c>
       <c r="O18" s="4">
         <f t="shared" ca="1" si="17"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="X18">
         <f t="shared" ca="1" si="12"/>
-        <v>144000</v>
+        <v>147500</v>
       </c>
       <c r="Y18">
         <f t="shared" ca="1" si="13"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AD18" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[5,4,8,240,10,4000],</v>
+        <v>[5,4,8,240,10,6000],</v>
       </c>
       <c r="AG18" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="L19" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>49000</v>
+        <v>63000</v>
       </c>
       <c r="M19" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="N19" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>34000</v>
+        <v>48000</v>
       </c>
       <c r="O19" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>90</v>
       </c>
       <c r="Q19" s="10">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="R19" s="13">
-        <v>4.9751243781094523</v>
+        <v>4.8899755501222497</v>
       </c>
       <c r="S19">
         <f t="shared" si="7"/>
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="T19">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="U19">
         <f t="shared" si="9"/>
@@ -3059,19 +3059,19 @@
       </c>
       <c r="V19">
         <f t="shared" ca="1" si="10"/>
-        <v>2010</v>
+        <v>2045</v>
       </c>
       <c r="W19">
         <f t="shared" ca="1" si="11"/>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="X19">
         <f t="shared" ca="1" si="12"/>
-        <v>154000</v>
+        <v>157500</v>
       </c>
       <c r="Y19">
         <f t="shared" ca="1" si="13"/>
-        <v>3425</v>
+        <v>3500</v>
       </c>
       <c r="Z19" s="4">
         <f t="shared" ca="1" si="13"/>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AA19" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>1325</v>
+        <v>1400</v>
       </c>
       <c r="AD19" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="L20" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>55000</v>
+        <v>69000</v>
       </c>
       <c r="M20" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -3137,53 +3137,53 @@
       </c>
       <c r="N20" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>40000</v>
+        <v>54000</v>
       </c>
       <c r="O20" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>110</v>
       </c>
       <c r="Q20" s="10">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="R20" s="13">
-        <v>4.9019607843137258</v>
+        <v>4.71976401179941</v>
       </c>
       <c r="S20">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="T20">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="U20">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V20">
         <f t="shared" ca="1" si="10"/>
-        <v>2040</v>
+        <v>1695</v>
       </c>
       <c r="W20">
         <f t="shared" ca="1" si="11"/>
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="X20">
         <f t="shared" ca="1" si="12"/>
-        <v>164000</v>
+        <v>165500</v>
       </c>
       <c r="Y20">
         <f t="shared" ca="1" si="13"/>
-        <v>3550</v>
+        <v>3520</v>
       </c>
       <c r="Z20" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>80000</v>
+        <v>78000</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="AD20" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="L21" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>61000</v>
+        <v>75000</v>
       </c>
       <c r="M21" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -3241,53 +3241,53 @@
       </c>
       <c r="N21" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>46000</v>
+        <v>60000</v>
       </c>
       <c r="O21" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>130</v>
       </c>
       <c r="Q21" s="10">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="R21" s="13">
-        <v>4.8899755501222497</v>
+        <v>4.6109510086455332</v>
       </c>
       <c r="S21">
         <f t="shared" si="7"/>
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="T21">
         <f t="shared" si="8"/>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="U21">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V21">
         <f t="shared" ca="1" si="10"/>
-        <v>2045</v>
+        <v>1735</v>
       </c>
       <c r="W21">
         <f t="shared" ca="1" si="11"/>
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="X21">
         <f t="shared" ca="1" si="12"/>
-        <v>174000</v>
+        <v>173500</v>
       </c>
       <c r="Y21">
         <f t="shared" ca="1" si="13"/>
-        <v>3750</v>
+        <v>3540</v>
       </c>
       <c r="Z21" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>90000</v>
+        <v>86000</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>1650</v>
+        <v>1440</v>
       </c>
       <c r="AD21" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L22" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>67000</v>
+        <v>81000</v>
       </c>
       <c r="M22" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -3345,53 +3345,53 @@
       </c>
       <c r="N22" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>52000</v>
+        <v>66000</v>
       </c>
       <c r="O22" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>150</v>
       </c>
       <c r="Q22" s="10">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="R22" s="13">
-        <v>4.8076923076923075</v>
+        <v>4.507042253521127</v>
       </c>
       <c r="S22">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="T22">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="U22">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V22">
         <f t="shared" ca="1" si="10"/>
-        <v>2080</v>
+        <v>1775</v>
       </c>
       <c r="W22">
         <f t="shared" ca="1" si="11"/>
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="X22">
         <f t="shared" ca="1" si="12"/>
-        <v>184000</v>
+        <v>181500</v>
       </c>
       <c r="Y22">
         <f t="shared" ca="1" si="13"/>
-        <v>3875</v>
+        <v>3560</v>
       </c>
       <c r="Z22" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>100000</v>
+        <v>94000</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>1775</v>
+        <v>1460</v>
       </c>
       <c r="AD22" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="L23" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>73000</v>
+        <v>87000</v>
       </c>
       <c r="M23" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -3449,53 +3449,53 @@
       </c>
       <c r="N23" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>58000</v>
+        <v>72000</v>
       </c>
       <c r="O23" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>170</v>
       </c>
       <c r="Q23" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R23" s="13">
-        <v>4.7058823529411766</v>
+        <v>4.4943820224719104</v>
       </c>
       <c r="S23">
         <f t="shared" si="7"/>
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="T23">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="U23">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V23">
         <f t="shared" ca="1" si="10"/>
-        <v>2125</v>
+        <v>1780</v>
       </c>
       <c r="W23">
         <f t="shared" ca="1" si="11"/>
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="X23">
         <f t="shared" ca="1" si="12"/>
-        <v>194000</v>
+        <v>189500</v>
       </c>
       <c r="Y23">
         <f t="shared" ca="1" si="13"/>
-        <v>4000</v>
+        <v>3580</v>
       </c>
       <c r="Z23" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>110000</v>
+        <v>102000</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>1900</v>
+        <v>1480</v>
       </c>
       <c r="AD23" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L24" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>79000</v>
+        <v>93000</v>
       </c>
       <c r="M24" s="4">
         <f t="shared" ca="1" si="6"/>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="N24" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>64000</v>
+        <v>78000</v>
       </c>
       <c r="O24" s="4">
         <f t="shared" ca="1" si="17"/>
         <v>190</v>
       </c>
       <c r="Q24" s="10">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="R24" s="13">
-        <v>4.6082949308755756</v>
+        <v>4.4642857142857144</v>
       </c>
       <c r="S24">
         <f t="shared" si="7"/>
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="T24">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="U24">
         <f t="shared" si="9"/>
@@ -3579,27 +3579,27 @@
       </c>
       <c r="V24">
         <f t="shared" ca="1" si="10"/>
-        <v>2170</v>
+        <v>2240</v>
       </c>
       <c r="W24">
         <f t="shared" ca="1" si="11"/>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="X24">
         <f t="shared" ca="1" si="12"/>
-        <v>204000</v>
+        <v>199500</v>
       </c>
       <c r="Y24">
         <f t="shared" ca="1" si="13"/>
-        <v>4125</v>
+        <v>3680</v>
       </c>
       <c r="Z24" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>120000</v>
+        <v>112000</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2025</v>
+        <v>1580</v>
       </c>
       <c r="AD24" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -3630,84 +3630,84 @@
         <v>200</v>
       </c>
       <c r="G25" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H25" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1825</v>
+        <v>1775</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K25" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.2876712328767121</v>
+        <v>4.507042253521127</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>85000</v>
+        <v>101000</v>
       </c>
       <c r="M25" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="N25" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>70000</v>
+        <v>86000</v>
       </c>
       <c r="O25" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="Q25" s="10">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R25" s="13">
-        <v>4.5454545454545459</v>
+        <v>4.4568245125348191</v>
       </c>
       <c r="S25">
         <f t="shared" si="7"/>
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="T25">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="U25">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V25">
         <f t="shared" ca="1" si="10"/>
-        <v>2200</v>
+        <v>1795</v>
       </c>
       <c r="W25">
         <f t="shared" ca="1" si="11"/>
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="X25">
         <f t="shared" ca="1" si="12"/>
-        <v>214000</v>
+        <v>207500</v>
       </c>
       <c r="Y25">
         <f t="shared" ca="1" si="13"/>
-        <v>4250</v>
+        <v>3700</v>
       </c>
       <c r="Z25" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>130000</v>
+        <v>120000</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2150</v>
+        <v>1600</v>
       </c>
       <c r="AD25" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,8,1,200,30,6000],</v>
+        <v>[6,8,1,200,20,8000],</v>
       </c>
       <c r="AG25" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3734,44 +3734,44 @@
         <v>210</v>
       </c>
       <c r="G26" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H26" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1890</v>
+        <v>1840</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K26" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.1746031746031744</v>
+        <v>4.3478260869565215</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>91000</v>
+        <v>109000</v>
       </c>
       <c r="M26" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="N26" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>76000</v>
+        <v>94000</v>
       </c>
       <c r="O26" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="Q26" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R26" s="13">
-        <v>4.4642857142857144</v>
+        <v>4.395604395604396</v>
       </c>
       <c r="S26">
         <f t="shared" si="7"/>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="V26">
         <f t="shared" ca="1" si="10"/>
-        <v>2240</v>
+        <v>2275</v>
       </c>
       <c r="W26">
         <f t="shared" ca="1" si="11"/>
@@ -3795,23 +3795,23 @@
       </c>
       <c r="X26">
         <f t="shared" ca="1" si="12"/>
-        <v>224000</v>
+        <v>217500</v>
       </c>
       <c r="Y26">
         <f t="shared" ca="1" si="13"/>
-        <v>4350</v>
+        <v>3800</v>
       </c>
       <c r="Z26" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>140000</v>
+        <v>130000</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2250</v>
+        <v>1700</v>
       </c>
       <c r="AD26" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[9,1,2,210,30,6000],</v>
+        <v>[9,1,2,210,20,8000],</v>
       </c>
       <c r="AG26" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3838,44 +3838,44 @@
         <v>200</v>
       </c>
       <c r="G27" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H27" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1830</v>
+        <v>1780</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K27" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.278688524590164</v>
+        <v>4.4943820224719104</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>97000</v>
+        <v>117000</v>
       </c>
       <c r="M27" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="N27" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>82000</v>
+        <v>102000</v>
       </c>
       <c r="O27" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="Q27" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R27" s="13">
-        <v>4.395604395604396</v>
+        <v>4.3478260869565215</v>
       </c>
       <c r="S27">
         <f t="shared" si="7"/>
@@ -3883,39 +3883,39 @@
       </c>
       <c r="T27">
         <f t="shared" si="8"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="U27">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V27">
         <f t="shared" ca="1" si="10"/>
-        <v>2275</v>
+        <v>1840</v>
       </c>
       <c r="W27">
         <f t="shared" ca="1" si="11"/>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X27">
         <f t="shared" ca="1" si="12"/>
-        <v>234000</v>
+        <v>225500</v>
       </c>
       <c r="Y27">
         <f t="shared" ca="1" si="13"/>
-        <v>4450</v>
+        <v>3820</v>
       </c>
       <c r="Z27" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>150000</v>
+        <v>138000</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2350</v>
+        <v>1720</v>
       </c>
       <c r="AD27" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[10,2,4,200,30,6000],</v>
+        <v>[10,2,4,200,20,8000],</v>
       </c>
       <c r="AG27" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -3942,38 +3942,38 @@
         <v>190</v>
       </c>
       <c r="G28" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H28" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1745</v>
+        <v>1695</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K28" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4383954154727792</v>
+        <v>4.71976401179941</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>103000</v>
+        <v>125000</v>
       </c>
       <c r="M28" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="N28" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>88000</v>
+        <v>110000</v>
       </c>
       <c r="O28" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="Q28" s="10">
         <v>27</v>
@@ -4003,23 +4003,23 @@
       </c>
       <c r="X28">
         <f t="shared" ca="1" si="12"/>
-        <v>244000</v>
+        <v>235500</v>
       </c>
       <c r="Y28">
         <f t="shared" ca="1" si="13"/>
-        <v>4550</v>
+        <v>3920</v>
       </c>
       <c r="Z28" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>160000</v>
+        <v>148000</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2450</v>
+        <v>1820</v>
       </c>
       <c r="AD28" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[8,4,3,190,30,6000],</v>
+        <v>[8,4,3,190,20,8000],</v>
       </c>
       <c r="AG28" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4046,48 +4046,48 @@
         <v>200</v>
       </c>
       <c r="G29" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H29" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1845</v>
+        <v>1795</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K29" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.2520325203252032</v>
+        <v>4.4568245125348191</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>109000</v>
+        <v>133000</v>
       </c>
       <c r="M29" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="N29" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>94000</v>
+        <v>118000</v>
       </c>
       <c r="O29" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="Q29" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R29" s="13">
-        <v>4.2283298097251585</v>
+        <v>4.2440318302387272</v>
       </c>
       <c r="S29">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="T29">
         <f t="shared" si="8"/>
@@ -4095,35 +4095,35 @@
       </c>
       <c r="U29">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V29">
         <f t="shared" ca="1" si="10"/>
-        <v>2365</v>
+        <v>1885</v>
       </c>
       <c r="W29">
         <f t="shared" ca="1" si="11"/>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="X29">
         <f t="shared" ca="1" si="12"/>
-        <v>254000</v>
+        <v>243500</v>
       </c>
       <c r="Y29">
         <f t="shared" ca="1" si="13"/>
-        <v>4650</v>
+        <v>4020</v>
       </c>
       <c r="Z29" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>170000</v>
+        <v>156000</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2550</v>
+        <v>1920</v>
       </c>
       <c r="AD29" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[11,6,2,200,30,6000],</v>
+        <v>[11,6,2,200,20,8000],</v>
       </c>
       <c r="AG29" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4150,84 +4150,84 @@
         <v>210</v>
       </c>
       <c r="G30" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H30" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1940</v>
+        <v>1890</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.0927835051546393</v>
+        <v>4.2328042328042326</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>115000</v>
+        <v>141000</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="N30" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>100000</v>
+        <v>126000</v>
       </c>
       <c r="O30" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="Q30" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="R30" s="13">
-        <v>4.1841004184100417</v>
+        <v>4.2328042328042326</v>
       </c>
       <c r="S30">
         <f t="shared" si="7"/>
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="T30">
         <f t="shared" si="8"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="U30">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="V30">
         <f t="shared" ca="1" si="10"/>
-        <v>2390</v>
+        <v>1890</v>
       </c>
       <c r="W30">
         <f t="shared" ca="1" si="11"/>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X30">
         <f t="shared" ca="1" si="12"/>
-        <v>264000</v>
+        <v>251500</v>
       </c>
       <c r="Y30">
         <f t="shared" ca="1" si="13"/>
-        <v>4750</v>
+        <v>4040</v>
       </c>
       <c r="Z30" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>180000</v>
+        <v>164000</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2650</v>
+        <v>1940</v>
       </c>
       <c r="AD30" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,8,8,210,30,6000],</v>
+        <v>[6,8,8,210,20,8000],</v>
       </c>
       <c r="AG30" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4254,48 +4254,48 @@
         <v>200</v>
       </c>
       <c r="G31" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H31" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>1785</v>
+        <v>1735</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K31" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3613445378151261</v>
+        <v>4.6109510086455332</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>121000</v>
+        <v>149000</v>
       </c>
       <c r="M31" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="N31" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>106000</v>
+        <v>134000</v>
       </c>
       <c r="O31" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="Q31" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R31" s="13">
-        <v>4.1152263374485596</v>
+        <v>4.2283298097251585</v>
       </c>
       <c r="S31">
         <f t="shared" si="7"/>
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="T31">
         <f t="shared" si="8"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="V31">
         <f t="shared" ca="1" si="10"/>
-        <v>2430</v>
+        <v>2365</v>
       </c>
       <c r="W31">
         <f t="shared" ca="1" si="11"/>
@@ -4315,23 +4315,23 @@
       </c>
       <c r="X31">
         <f t="shared" ca="1" si="12"/>
-        <v>274000</v>
+        <v>261500</v>
       </c>
       <c r="Y31">
         <f t="shared" ca="1" si="13"/>
-        <v>4850</v>
+        <v>4140</v>
       </c>
       <c r="Z31" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>190000</v>
+        <v>174000</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2750</v>
+        <v>2040</v>
       </c>
       <c r="AD31" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[5,1,1,200,30,6000],</v>
+        <v>[5,1,1,200,20,8000],</v>
       </c>
       <c r="AG31" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -4377,61 +4377,61 @@
       </c>
       <c r="L32" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>131000</v>
+        <v>159000</v>
       </c>
       <c r="M32" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="N32" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>116000</v>
+        <v>144000</v>
       </c>
       <c r="O32" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="Q32" s="10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R32" s="13">
-        <v>3.4383954154727792</v>
+        <v>4.1841004184100417</v>
       </c>
       <c r="S32">
         <f t="shared" si="7"/>
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="T32">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="U32">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="V32">
         <f t="shared" ca="1" si="10"/>
-        <v>1745</v>
+        <v>2390</v>
       </c>
       <c r="W32">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X32">
         <f t="shared" ca="1" si="12"/>
-        <v>280000</v>
+        <v>271500</v>
       </c>
       <c r="Y32">
         <f t="shared" ca="1" si="13"/>
-        <v>4880</v>
+        <v>4240</v>
       </c>
       <c r="Z32" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>196000</v>
+        <v>184000</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2780</v>
+        <v>2140</v>
       </c>
       <c r="AD32" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -4481,61 +4481,61 @@
       </c>
       <c r="L33" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>141000</v>
+        <v>169000</v>
       </c>
       <c r="M33" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="N33" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>126000</v>
+        <v>154000</v>
       </c>
       <c r="O33" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="Q33" s="10">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="R33" s="13">
-        <v>3.3613445378151261</v>
+        <v>4.1775456919060057</v>
       </c>
       <c r="S33">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="T33">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="U33">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="V33">
         <f t="shared" ca="1" si="10"/>
-        <v>1785</v>
+        <v>1915</v>
       </c>
       <c r="W33">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="X33">
         <f t="shared" ca="1" si="12"/>
-        <v>286000</v>
+        <v>279500</v>
       </c>
       <c r="Y33">
         <f t="shared" ca="1" si="13"/>
-        <v>4910</v>
+        <v>4340</v>
       </c>
       <c r="Z33" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>202000</v>
+        <v>192000</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2810</v>
+        <v>2240</v>
       </c>
       <c r="AD33" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -4585,61 +4585,61 @@
       </c>
       <c r="L34" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>151000</v>
+        <v>179000</v>
       </c>
       <c r="M34" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="N34" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>136000</v>
+        <v>164000</v>
       </c>
       <c r="O34" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="Q34" s="10">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R34" s="13">
-        <v>3.2876712328767121</v>
+        <v>4.1152263374485596</v>
       </c>
       <c r="S34">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="T34">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="U34">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="V34">
         <f t="shared" ca="1" si="10"/>
-        <v>1825</v>
+        <v>2430</v>
       </c>
       <c r="W34">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X34">
         <f t="shared" ca="1" si="12"/>
-        <v>292000</v>
+        <v>289500</v>
       </c>
       <c r="Y34">
         <f t="shared" ca="1" si="13"/>
-        <v>4940</v>
+        <v>4440</v>
       </c>
       <c r="Z34" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>208000</v>
+        <v>202000</v>
       </c>
       <c r="AA34" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2840</v>
+        <v>2340</v>
       </c>
       <c r="AD34" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -4689,61 +4689,61 @@
       </c>
       <c r="L35" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>161000</v>
+        <v>189000</v>
       </c>
       <c r="M35" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>800</v>
+        <v>730</v>
       </c>
       <c r="N35" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>146000</v>
+        <v>174000</v>
       </c>
       <c r="O35" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>800</v>
+        <v>730</v>
       </c>
       <c r="Q35" s="10">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="R35" s="13">
-        <v>3.278688524590164</v>
+        <v>4.0920716112531972</v>
       </c>
       <c r="S35">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="T35">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="U35">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="V35">
         <f t="shared" ca="1" si="10"/>
-        <v>1830</v>
+        <v>1955</v>
       </c>
       <c r="W35">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="X35">
         <f t="shared" ca="1" si="12"/>
-        <v>298000</v>
+        <v>297500</v>
       </c>
       <c r="Y35">
         <f t="shared" ca="1" si="13"/>
-        <v>4970</v>
+        <v>4540</v>
       </c>
       <c r="Z35" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>214000</v>
+        <v>210000</v>
       </c>
       <c r="AA35" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2870</v>
+        <v>2440</v>
       </c>
       <c r="AD35" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -4793,61 +4793,61 @@
       </c>
       <c r="L36" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>171000</v>
+        <v>199000</v>
       </c>
       <c r="M36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>900</v>
+        <v>830</v>
       </c>
       <c r="N36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>156000</v>
+        <v>184000</v>
       </c>
       <c r="O36" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>900</v>
+        <v>830</v>
       </c>
       <c r="Q36" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R36" s="13">
-        <v>3.2520325203252032</v>
+        <v>4</v>
       </c>
       <c r="S36">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="T36">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="U36">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="V36">
         <f t="shared" ca="1" si="10"/>
-        <v>1845</v>
+        <v>2000</v>
       </c>
       <c r="W36">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="X36">
         <f t="shared" ca="1" si="12"/>
-        <v>304000</v>
+        <v>305500</v>
       </c>
       <c r="Y36">
         <f t="shared" ca="1" si="13"/>
-        <v>5000</v>
+        <v>4640</v>
       </c>
       <c r="Z36" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>220000</v>
+        <v>218000</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2900</v>
+        <v>2540</v>
       </c>
       <c r="AD36" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -4897,53 +4897,53 @@
       </c>
       <c r="L37" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>181000</v>
+        <v>209000</v>
       </c>
       <c r="M37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="N37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>166000</v>
+        <v>194000</v>
       </c>
       <c r="O37" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="Q37" s="10">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="R37" s="13">
-        <v>3.225806451612903</v>
+        <v>3.9119804400977993</v>
       </c>
       <c r="S37">
         <f t="shared" si="7"/>
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="T37">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="U37">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="V37">
         <f t="shared" ca="1" si="10"/>
-        <v>1860</v>
+        <v>2045</v>
       </c>
       <c r="W37">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="X37">
         <f t="shared" ca="1" si="12"/>
-        <v>310000</v>
+        <v>313500</v>
       </c>
       <c r="Y37">
         <f t="shared" ca="1" si="13"/>
-        <v>5020</v>
+        <v>4740</v>
       </c>
       <c r="Z37" s="4">
         <f t="shared" ca="1" si="13"/>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AA37" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2920</v>
+        <v>2640</v>
       </c>
       <c r="AD37" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -4982,14 +4982,14 @@
         <v>180</v>
       </c>
       <c r="G38" s="4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H38" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>2125</v>
+        <v>2000</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
@@ -4997,69 +4997,69 @@
       </c>
       <c r="K38" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>4.7058823529411766</v>
+        <v>4</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>191000</v>
+        <v>217000</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1125</v>
+        <v>1030</v>
       </c>
       <c r="N38" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>176000</v>
+        <v>202000</v>
       </c>
       <c r="O38" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1125</v>
+        <v>1030</v>
       </c>
       <c r="Q38" s="10">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="R38" s="13">
-        <v>3.1746031746031744</v>
+        <v>3.8554216867469879</v>
       </c>
       <c r="S38">
         <f t="shared" si="7"/>
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="T38">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="U38">
         <f t="shared" si="9"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="V38">
         <f t="shared" ca="1" si="10"/>
-        <v>1890</v>
+        <v>2075</v>
       </c>
       <c r="W38">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="X38">
         <f t="shared" ca="1" si="12"/>
-        <v>316000</v>
+        <v>321500</v>
       </c>
       <c r="Y38">
         <f t="shared" ca="1" si="13"/>
-        <v>5050</v>
+        <v>4840</v>
       </c>
       <c r="Z38" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>232000</v>
+        <v>234000</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2950</v>
+        <v>2740</v>
       </c>
       <c r="AD38" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,4,2,180,125,10000],</v>
+        <v>[6,4,2,180,100,8000],</v>
       </c>
       <c r="AG38" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -5086,14 +5086,14 @@
         <v>170</v>
       </c>
       <c r="G39" s="4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H39" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>2080</v>
+        <v>1955</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ca="1" si="3"/>
@@ -5101,33 +5101,33 @@
       </c>
       <c r="K39" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>4.8076923076923075</v>
+        <v>4.0920716112531972</v>
       </c>
       <c r="L39" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>201000</v>
+        <v>225000</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1250</v>
+        <v>1130</v>
       </c>
       <c r="N39" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>186000</v>
+        <v>210000</v>
       </c>
       <c r="O39" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1250</v>
+        <v>1130</v>
       </c>
       <c r="Q39" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R39" s="13">
-        <v>3.0927835051546393</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="S39">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="T39">
         <f t="shared" si="8"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="V39">
         <f t="shared" ca="1" si="10"/>
-        <v>1940</v>
+        <v>1860</v>
       </c>
       <c r="W39">
         <f t="shared" ca="1" si="11"/>
@@ -5147,23 +5147,23 @@
       </c>
       <c r="X39">
         <f t="shared" ca="1" si="12"/>
-        <v>322000</v>
+        <v>327500</v>
       </c>
       <c r="Y39">
         <f t="shared" ca="1" si="13"/>
-        <v>5070</v>
+        <v>4860</v>
       </c>
       <c r="Z39" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>238000</v>
+        <v>240000</v>
       </c>
       <c r="AA39" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2970</v>
+        <v>2760</v>
       </c>
       <c r="AD39" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[9,6,4,170,125,10000],</v>
+        <v>[9,6,4,170,100,8000],</v>
       </c>
       <c r="AG39" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -5190,14 +5190,14 @@
         <v>160</v>
       </c>
       <c r="G40" s="4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H40" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>2010</v>
+        <v>1885</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="3"/>
@@ -5205,37 +5205,37 @@
       </c>
       <c r="K40" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>4.9751243781094523</v>
+        <v>4.2440318302387272</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>211000</v>
+        <v>233000</v>
       </c>
       <c r="M40" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1375</v>
+        <v>1230</v>
       </c>
       <c r="N40" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>196000</v>
+        <v>218000</v>
       </c>
       <c r="O40" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1375</v>
+        <v>1230</v>
       </c>
       <c r="Q40" s="10">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="R40" s="13">
-        <v>3.0927835051546393</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="S40">
         <f t="shared" si="7"/>
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="T40">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <f t="shared" si="9"/>
@@ -5243,31 +5243,31 @@
       </c>
       <c r="V40">
         <f t="shared" ca="1" si="10"/>
-        <v>1940</v>
+        <v>1860</v>
       </c>
       <c r="W40">
         <f t="shared" ca="1" si="11"/>
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="X40">
         <f t="shared" ca="1" si="12"/>
-        <v>328000</v>
+        <v>333500</v>
       </c>
       <c r="Y40">
         <f t="shared" ca="1" si="13"/>
-        <v>5100</v>
+        <v>4870</v>
       </c>
       <c r="Z40" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>244000</v>
+        <v>246000</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3000</v>
+        <v>2770</v>
       </c>
       <c r="AD40" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[10,8,3,160,125,10000],</v>
+        <v>[10,8,3,160,100,8000],</v>
       </c>
       <c r="AG40" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -5294,14 +5294,14 @@
         <v>190</v>
       </c>
       <c r="G41" s="4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H41" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>2200</v>
+        <v>2075</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="3"/>
@@ -5309,37 +5309,37 @@
       </c>
       <c r="K41" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>4.5454545454545459</v>
+        <v>3.8554216867469879</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>221000</v>
+        <v>241000</v>
       </c>
       <c r="M41" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1500</v>
+        <v>1330</v>
       </c>
       <c r="N41" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>206000</v>
+        <v>226000</v>
       </c>
       <c r="O41" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1500</v>
+        <v>1330</v>
       </c>
       <c r="Q41" s="10">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R41" s="13">
-        <v>2.9776674937965262</v>
+        <v>3.1413612565445028</v>
       </c>
       <c r="S41">
         <f t="shared" si="7"/>
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="T41">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U41">
         <f t="shared" si="9"/>
@@ -5347,31 +5347,31 @@
       </c>
       <c r="V41">
         <f t="shared" ca="1" si="10"/>
-        <v>2015</v>
+        <v>1910</v>
       </c>
       <c r="W41">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="X41">
         <f t="shared" ca="1" si="12"/>
-        <v>334000</v>
+        <v>339500</v>
       </c>
       <c r="Y41">
         <f t="shared" ca="1" si="13"/>
-        <v>5120</v>
+        <v>4880</v>
       </c>
       <c r="Z41" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>250000</v>
+        <v>252000</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3020</v>
+        <v>2780</v>
       </c>
       <c r="AD41" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[8,1,2,190,125,10000],</v>
+        <v>[8,1,2,190,100,8000],</v>
       </c>
       <c r="AG41" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -5398,14 +5398,14 @@
         <v>180</v>
       </c>
       <c r="G42" s="4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H42" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>2170</v>
+        <v>2045</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="3"/>
@@ -5413,33 +5413,33 @@
       </c>
       <c r="K42" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>4.6082949308755756</v>
+        <v>3.9119804400977993</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>231000</v>
+        <v>249000</v>
       </c>
       <c r="M42" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1625</v>
+        <v>1430</v>
       </c>
       <c r="N42" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>216000</v>
+        <v>234000</v>
       </c>
       <c r="O42" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1625</v>
+        <v>1430</v>
       </c>
       <c r="Q42" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R42" s="13">
-        <v>2.8708133971291865</v>
+        <v>3.0927835051546393</v>
       </c>
       <c r="S42">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="T42">
         <f t="shared" si="8"/>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="V42">
         <f t="shared" ca="1" si="10"/>
-        <v>2090</v>
+        <v>1940</v>
       </c>
       <c r="W42">
         <f t="shared" ca="1" si="11"/>
@@ -5459,23 +5459,23 @@
       </c>
       <c r="X42">
         <f t="shared" ca="1" si="12"/>
-        <v>340000</v>
+        <v>345500</v>
       </c>
       <c r="Y42">
         <f t="shared" ca="1" si="13"/>
-        <v>5140</v>
+        <v>4900</v>
       </c>
       <c r="Z42" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>256000</v>
+        <v>258000</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3040</v>
+        <v>2800</v>
       </c>
       <c r="AD42" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[11,2,8,180,125,10000],</v>
+        <v>[11,2,8,180,100,8000],</v>
       </c>
       <c r="AG42" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -5502,14 +5502,14 @@
         <v>170</v>
       </c>
       <c r="G43" s="4">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H43" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>2040</v>
+        <v>1915</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ca="1" si="3"/>
@@ -5517,37 +5517,37 @@
       </c>
       <c r="K43" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>4.9019607843137258</v>
+        <v>4.1775456919060057</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>241000</v>
+        <v>257000</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1750</v>
+        <v>1530</v>
       </c>
       <c r="N43" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>226000</v>
+        <v>242000</v>
       </c>
       <c r="O43" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1750</v>
+        <v>1530</v>
       </c>
       <c r="Q43" s="10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="R43" s="13">
-        <v>2.8235294117647061</v>
+        <v>3.053435114503817</v>
       </c>
       <c r="S43">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="T43">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U43">
         <f t="shared" si="9"/>
@@ -5555,31 +5555,31 @@
       </c>
       <c r="V43">
         <f t="shared" ca="1" si="10"/>
-        <v>2125</v>
+        <v>1965</v>
       </c>
       <c r="W43">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="X43">
         <f t="shared" ca="1" si="12"/>
-        <v>346000</v>
+        <v>351500</v>
       </c>
       <c r="Y43">
         <f t="shared" ca="1" si="13"/>
-        <v>5160</v>
+        <v>4910</v>
       </c>
       <c r="Z43" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>262000</v>
+        <v>264000</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3060</v>
+        <v>2810</v>
       </c>
       <c r="AD43" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,4,1,170,125,10000],</v>
+        <v>[6,4,1,170,100,8000],</v>
       </c>
       <c r="AG43" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -5625,33 +5625,33 @@
       </c>
       <c r="L44" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>251000</v>
+        <v>267000</v>
       </c>
       <c r="M44" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>1950</v>
+        <v>1730</v>
       </c>
       <c r="N44" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>236000</v>
+        <v>252000</v>
       </c>
       <c r="O44" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>1950</v>
+        <v>1730</v>
       </c>
       <c r="Q44" s="10">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R44" s="13">
-        <v>2.7586206896551726</v>
+        <v>3.0456852791878171</v>
       </c>
       <c r="S44">
         <f t="shared" si="7"/>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="T44">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U44">
         <f t="shared" si="9"/>
@@ -5659,27 +5659,27 @@
       </c>
       <c r="V44">
         <f t="shared" ca="1" si="10"/>
-        <v>2175</v>
+        <v>1970</v>
       </c>
       <c r="W44">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="X44">
         <f t="shared" ca="1" si="12"/>
-        <v>352000</v>
+        <v>357500</v>
       </c>
       <c r="Y44">
         <f t="shared" ca="1" si="13"/>
-        <v>5180</v>
+        <v>4920</v>
       </c>
       <c r="Z44" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>268000</v>
+        <v>270000</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3080</v>
+        <v>2820</v>
       </c>
       <c r="AD44" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -5729,61 +5729,61 @@
       </c>
       <c r="L45" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>261000</v>
+        <v>277000</v>
       </c>
       <c r="M45" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>2150</v>
+        <v>1930</v>
       </c>
       <c r="N45" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>246000</v>
+        <v>262000</v>
       </c>
       <c r="O45" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>2150</v>
+        <v>1930</v>
       </c>
       <c r="Q45" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R45" s="13">
-        <v>2.150537634408602</v>
+        <v>2.9776674937965262</v>
       </c>
       <c r="S45">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="T45">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U45">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V45">
         <f t="shared" ca="1" si="10"/>
-        <v>1860</v>
+        <v>2015</v>
       </c>
       <c r="W45">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X45">
         <f t="shared" ca="1" si="12"/>
-        <v>356000</v>
+        <v>363500</v>
       </c>
       <c r="Y45">
         <f t="shared" ca="1" si="13"/>
-        <v>5190</v>
+        <v>4940</v>
       </c>
       <c r="Z45" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>272000</v>
+        <v>276000</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3090</v>
+        <v>2840</v>
       </c>
       <c r="AD45" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -5833,29 +5833,29 @@
       </c>
       <c r="L46" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>271000</v>
+        <v>287000</v>
       </c>
       <c r="M46" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>2350</v>
+        <v>2130</v>
       </c>
       <c r="N46" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>256000</v>
+        <v>272000</v>
       </c>
       <c r="O46" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>2350</v>
+        <v>2130</v>
       </c>
       <c r="Q46" s="10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R46" s="13">
-        <v>2.0942408376963351</v>
+        <v>2.9411764705882355</v>
       </c>
       <c r="S46">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="T46">
         <f t="shared" si="8"/>
@@ -5863,31 +5863,31 @@
       </c>
       <c r="U46">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V46">
         <f t="shared" ca="1" si="10"/>
-        <v>1910</v>
+        <v>2040</v>
       </c>
       <c r="W46">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="X46">
         <f t="shared" ca="1" si="12"/>
-        <v>360000</v>
+        <v>369500</v>
       </c>
       <c r="Y46">
         <f t="shared" ca="1" si="13"/>
-        <v>5200</v>
+        <v>4950</v>
       </c>
       <c r="Z46" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>276000</v>
+        <v>282000</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3100</v>
+        <v>2850</v>
       </c>
       <c r="AD46" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -5937,29 +5937,29 @@
       </c>
       <c r="L47" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>281000</v>
+        <v>297000</v>
       </c>
       <c r="M47" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>2550</v>
+        <v>2330</v>
       </c>
       <c r="N47" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>266000</v>
+        <v>282000</v>
       </c>
       <c r="O47" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>2550</v>
+        <v>2330</v>
       </c>
       <c r="Q47" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R47" s="13">
-        <v>2.0356234096692112</v>
+        <v>2.9197080291970803</v>
       </c>
       <c r="S47">
         <f t="shared" si="7"/>
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="T47">
         <f t="shared" si="8"/>
@@ -5967,31 +5967,31 @@
       </c>
       <c r="U47">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V47">
         <f t="shared" ca="1" si="10"/>
-        <v>1965</v>
+        <v>2055</v>
       </c>
       <c r="W47">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="X47">
         <f t="shared" ca="1" si="12"/>
-        <v>364000</v>
+        <v>375500</v>
       </c>
       <c r="Y47">
         <f t="shared" ca="1" si="13"/>
-        <v>5210</v>
+        <v>4960</v>
       </c>
       <c r="Z47" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>280000</v>
+        <v>288000</v>
       </c>
       <c r="AA47" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3110</v>
+        <v>2860</v>
       </c>
       <c r="AD47" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -6041,61 +6041,61 @@
       </c>
       <c r="L48" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>291000</v>
+        <v>307000</v>
       </c>
       <c r="M48" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>2750</v>
+        <v>2530</v>
       </c>
       <c r="N48" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>276000</v>
+        <v>292000</v>
       </c>
       <c r="O48" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>2750</v>
+        <v>2530</v>
       </c>
       <c r="Q48" s="10">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R48" s="13">
-        <v>2.030456852791878</v>
+        <v>2.8708133971291865</v>
       </c>
       <c r="S48">
         <f t="shared" si="7"/>
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="T48">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U48">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V48">
         <f t="shared" ca="1" si="10"/>
-        <v>1970</v>
+        <v>2090</v>
       </c>
       <c r="W48">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X48">
         <f t="shared" ca="1" si="12"/>
-        <v>368000</v>
+        <v>381500</v>
       </c>
       <c r="Y48">
         <f t="shared" ca="1" si="13"/>
-        <v>5220</v>
+        <v>4980</v>
       </c>
       <c r="Z48" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>284000</v>
+        <v>294000</v>
       </c>
       <c r="AA48" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3120</v>
+        <v>2880</v>
       </c>
       <c r="AD48" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -6145,25 +6145,25 @@
       </c>
       <c r="L49" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>301000</v>
+        <v>317000</v>
       </c>
       <c r="M49" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>2950</v>
+        <v>2730</v>
       </c>
       <c r="N49" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>286000</v>
+        <v>302000</v>
       </c>
       <c r="O49" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>2950</v>
+        <v>2730</v>
       </c>
       <c r="Q49" s="10">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="R49" s="13">
-        <v>1.9607843137254901</v>
+        <v>2.8235294117647061</v>
       </c>
       <c r="S49">
         <f t="shared" si="7"/>
@@ -6171,35 +6171,35 @@
       </c>
       <c r="T49">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U49">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V49">
         <f t="shared" ca="1" si="10"/>
-        <v>2040</v>
+        <v>2125</v>
       </c>
       <c r="W49">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X49">
         <f t="shared" ca="1" si="12"/>
-        <v>372000</v>
+        <v>387500</v>
       </c>
       <c r="Y49">
         <f t="shared" ca="1" si="13"/>
-        <v>5230</v>
+        <v>5000</v>
       </c>
       <c r="Z49" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>288000</v>
+        <v>300000</v>
       </c>
       <c r="AA49" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3130</v>
+        <v>2900</v>
       </c>
       <c r="AD49" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -6249,29 +6249,29 @@
       </c>
       <c r="L50" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>311000</v>
+        <v>327000</v>
       </c>
       <c r="M50" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="N50" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>296000</v>
+        <v>312000</v>
       </c>
       <c r="O50" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="Q50" s="10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R50" s="13">
-        <v>1.9464720194647203</v>
+        <v>2.8037383177570092</v>
       </c>
       <c r="S50">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="T50">
         <f t="shared" si="8"/>
@@ -6279,31 +6279,31 @@
       </c>
       <c r="U50">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V50">
         <f t="shared" ca="1" si="10"/>
-        <v>2055</v>
+        <v>2140</v>
       </c>
       <c r="W50">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="X50">
         <f t="shared" ca="1" si="12"/>
-        <v>376000</v>
+        <v>393500</v>
       </c>
       <c r="Y50">
         <f t="shared" ca="1" si="13"/>
-        <v>5240</v>
+        <v>5010</v>
       </c>
       <c r="Z50" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>292000</v>
+        <v>306000</v>
       </c>
       <c r="AA50" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3140</v>
+        <v>2910</v>
       </c>
       <c r="AD50" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -6337,7 +6337,7 @@
         <v>300</v>
       </c>
       <c r="H51" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6345,33 +6345,33 @@
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K51" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>5.6737588652482271</v>
+        <v>5.9101654846335698</v>
       </c>
       <c r="L51" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>323000</v>
+        <v>339500</v>
       </c>
       <c r="M51" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>3450</v>
+        <v>3230</v>
       </c>
       <c r="N51" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>308000</v>
+        <v>324500</v>
       </c>
       <c r="O51" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>3450</v>
+        <v>3230</v>
       </c>
       <c r="Q51" s="10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R51" s="13">
-        <v>1.8691588785046729</v>
+        <v>2.7586206896551726</v>
       </c>
       <c r="S51">
         <f t="shared" si="7"/>
@@ -6379,39 +6379,39 @@
       </c>
       <c r="T51">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U51">
         <f t="shared" si="9"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="V51">
         <f t="shared" ca="1" si="10"/>
-        <v>2140</v>
+        <v>2175</v>
       </c>
       <c r="W51">
         <f t="shared" ca="1" si="11"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X51">
         <f t="shared" ca="1" si="12"/>
-        <v>380000</v>
+        <v>399500</v>
       </c>
       <c r="Y51">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z51" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>296000</v>
+        <v>312000</v>
       </c>
       <c r="AA51" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD51" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,1,4,70,300,12000],</v>
+        <v>[6,1,4,70,300,12500],</v>
       </c>
       <c r="AG51" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6441,7 +6441,7 @@
         <v>300</v>
       </c>
       <c r="H52" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6449,27 +6449,27 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K52" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>6.0913705583756341</v>
+        <v>6.345177664974619</v>
       </c>
       <c r="L52" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>335000</v>
+        <v>352000</v>
       </c>
       <c r="M52" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>3750</v>
+        <v>3530</v>
       </c>
       <c r="N52" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>320000</v>
+        <v>337000</v>
       </c>
       <c r="O52" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>3750</v>
+        <v>3530</v>
       </c>
       <c r="Q52" s="10">
         <v>3</v>
@@ -6499,23 +6499,23 @@
       </c>
       <c r="X52">
         <f t="shared" ca="1" si="12"/>
-        <v>382500</v>
+        <v>402000</v>
       </c>
       <c r="Y52">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z52" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>298500</v>
+        <v>314500</v>
       </c>
       <c r="AA52" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD52" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[9,2,3,50,300,12000],</v>
+        <v>[9,2,3,50,300,12500],</v>
       </c>
       <c r="AG52" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6545,7 +6545,7 @@
         <v>300</v>
       </c>
       <c r="H53" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6553,27 +6553,27 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K53" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>5.8679706601466997</v>
+        <v>6.1124694376528117</v>
       </c>
       <c r="L53" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>347000</v>
+        <v>364500</v>
       </c>
       <c r="M53" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>4050</v>
+        <v>3830</v>
       </c>
       <c r="N53" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>332000</v>
+        <v>349500</v>
       </c>
       <c r="O53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>4050</v>
+        <v>3830</v>
       </c>
       <c r="Q53" s="10">
         <v>0</v>
@@ -6603,23 +6603,23 @@
       </c>
       <c r="X53">
         <f t="shared" ca="1" si="12"/>
-        <v>385000</v>
+        <v>404500</v>
       </c>
       <c r="Y53">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z53" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>301000</v>
+        <v>317000</v>
       </c>
       <c r="AA53" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD53" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[10,1,2,60,300,12000],</v>
+        <v>[10,1,2,60,300,12500],</v>
       </c>
       <c r="AG53" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6649,7 +6649,7 @@
         <v>300</v>
       </c>
       <c r="H54" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6657,27 +6657,27 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>6.0913705583756341</v>
+        <v>6.345177664974619</v>
       </c>
       <c r="L54" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>359000</v>
+        <v>377000</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>4350</v>
+        <v>4130</v>
       </c>
       <c r="N54" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>344000</v>
+        <v>362000</v>
       </c>
       <c r="O54" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>4350</v>
+        <v>4130</v>
       </c>
       <c r="Q54" s="10">
         <v>2</v>
@@ -6707,23 +6707,23 @@
       </c>
       <c r="X54">
         <f t="shared" ca="1" si="12"/>
-        <v>387500</v>
+        <v>407000</v>
       </c>
       <c r="Y54">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z54" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>303500</v>
+        <v>319500</v>
       </c>
       <c r="AA54" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD54" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[8,4,2,50,300,12000],</v>
+        <v>[8,4,2,50,300,12500],</v>
       </c>
       <c r="AG54" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6753,7 +6753,7 @@
         <v>300</v>
       </c>
       <c r="H55" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6761,27 +6761,27 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K55" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>6.1696658097686372</v>
+        <v>6.4267352185089974</v>
       </c>
       <c r="L55" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>371000</v>
+        <v>389500</v>
       </c>
       <c r="M55" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>4650</v>
+        <v>4430</v>
       </c>
       <c r="N55" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>356000</v>
+        <v>374500</v>
       </c>
       <c r="O55" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>4650</v>
+        <v>4430</v>
       </c>
       <c r="Q55" s="10">
         <v>4</v>
@@ -6811,23 +6811,23 @@
       </c>
       <c r="X55">
         <f t="shared" ca="1" si="12"/>
-        <v>390000</v>
+        <v>409500</v>
       </c>
       <c r="Y55">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z55" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>306000</v>
+        <v>322000</v>
       </c>
       <c r="AA55" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD55" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[11,6,8,40,300,12000],</v>
+        <v>[11,6,8,40,300,12500],</v>
       </c>
       <c r="AG55" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6857,7 +6857,7 @@
         <v>300</v>
       </c>
       <c r="H56" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6865,27 +6865,27 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>6.075949367088608</v>
+        <v>6.3291139240506329</v>
       </c>
       <c r="L56" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>383000</v>
+        <v>402000</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>4950</v>
+        <v>4730</v>
       </c>
       <c r="N56" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>368000</v>
+        <v>387000</v>
       </c>
       <c r="O56" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>4950</v>
+        <v>4730</v>
       </c>
       <c r="Q56" s="10">
         <v>1</v>
@@ -6915,23 +6915,23 @@
       </c>
       <c r="X56">
         <f t="shared" ca="1" si="12"/>
-        <v>392500</v>
+        <v>412000</v>
       </c>
       <c r="Y56">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z56" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>308500</v>
+        <v>324500</v>
       </c>
       <c r="AA56" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD56" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>[6,8,1,50,300,12000],</v>
+        <v>[6,8,1,50,300,12500],</v>
       </c>
       <c r="AG56" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6961,7 +6961,7 @@
         <v>300</v>
       </c>
       <c r="H57" s="4">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -6969,27 +6969,27 @@
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K57" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>6.6852367688022287</v>
+        <v>6.9637883008356543</v>
       </c>
       <c r="L57" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>395000</v>
+        <v>414500</v>
       </c>
       <c r="M57" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="N57" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>380000</v>
+        <v>399500</v>
       </c>
       <c r="O57" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Q57" s="10">
         <v>5</v>
@@ -7019,23 +7019,23 @@
       </c>
       <c r="X57">
         <f t="shared" ca="1" si="12"/>
-        <v>395000</v>
+        <v>414500</v>
       </c>
       <c r="Y57">
         <f t="shared" ca="1" si="13"/>
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="Z57" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>311000</v>
+        <v>327000</v>
       </c>
       <c r="AA57" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3150</v>
+        <v>2930</v>
       </c>
       <c r="AD57" s="4" t="str">
         <f ca="1">_xlfn.CONCAT("[",OFFSET(AD57,0,-27),",",OFFSET(AD57,0,-26),",",OFFSET(AD57,0,-25),",",OFFSET(AD57,0,-24),",",OFFSET(AD57,0,-23),",",OFFSET(AD57,0,-22),"],")</f>
-        <v>[5,2,4,30,300,12000],</v>
+        <v>[5,2,4,30,300,12500],</v>
       </c>
       <c r="AG57" s="4" t="str">
         <f t="shared" ca="1" si="15"/>
